--- a/AED.xlsx
+++ b/AED.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -445,8 +445,8 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,264 +489,231 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>熊本城 総合案内所</t>
+          <t>日田市役所</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>熊本県熊本市中央区本丸1-1</t>
+          <t>大分県日田市田島2丁目6-1</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>32.8063</v>
+        <v>33.323</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>130.7058</v>
+        <v>130.9408</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>総合案内所内</t>
+          <t>庁舎内</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>9:00-17:00</t>
+          <t>平日 8:30-17:15</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>サンプル(要差し替え)</t>
+          <t>サンプル(座標は概算・要差し替え)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>熊本市役所</t>
+          <t>JR日田駅</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>熊本県熊本市中央区手取本町1-1</t>
+          <t>大分県日田市元町</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>32.8031</v>
+        <v>33.3214</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>130.7079</v>
+        <v>130.9392</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1階ロビー</t>
+          <t>駅構内</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>平日 8:30-17:15</t>
+          <t>始発-終電</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>サンプル(要差し替え)</t>
+          <t>サンプル(座標は概算・要差し替え)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>JR熊本駅</t>
+          <t>日田市観光案内所</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>熊本県熊本市西区春日3丁目</t>
+          <t>大分県日田市元町(日田駅構内)</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>32.79</v>
+        <v>33.3212</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>130.689</v>
+        <v>130.9389</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>改札付近</t>
+          <t>案内所内</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>始発-終電</t>
+          <t>営業時間内</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>サンプル(要差し替え)</t>
+          <t>サンプル(座標は概算・要差し替え)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>桜町バスターミナル</t>
+          <t>パトリア日田</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>熊本県熊本市中央区桜町3-10</t>
+          <t>大分県日田市三本松</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>32.8021</v>
+        <v>33.3195</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>130.7007</v>
+        <v>130.94</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1階案内所</t>
+          <t>館内受付</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6:00-22:00</t>
+          <t>施設の開館時間内</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>サンプル(要差し替え)</t>
+          <t>サンプル(座標は概算・要差し替え)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>水前寺成趣園</t>
+          <t>豆田町 観光案内所</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>熊本県熊本市中央区水前寺公園8-1</t>
+          <t>大分県日田市豆田町</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>32.7878</v>
+        <v>33.325</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>130.7288</v>
+        <v>130.944</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>入口事務所</t>
+          <t>案内所内</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8:30-17:00</t>
+          <t>営業時間内</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>サンプル(要差し替え)</t>
+          <t>サンプル(座標は概算・要差し替え)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>熊本県庁</t>
+          <t>咸宜園跡</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>熊本県熊本市中央区水前寺6-18-1</t>
+          <t>大分県日田市淡窓</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>32.7898</v>
+        <v>33.3263</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>130.7417</v>
+        <v>130.9433</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1階受付</t>
+          <t>管理棟</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>平日 8:30-17:15</t>
+          <t>開園時間内</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>サンプル(要差し替え)</t>
+          <t>サンプル(座標は概算・要差し替え)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>熊本大学 黒髪キャンパス</t>
+          <t>日田温泉 三隈川沿い</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>熊本県熊本市中央区黒髪2-39-1</t>
+          <t>大分県日田市隈</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>32.8125</v>
+        <v>33.3265</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>130.7274</v>
+        <v>130.9475</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>事務棟入口</t>
+          <t>受付付近</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>平日 8:30-17:00</t>
+          <t>施設の営業時間内</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>サンプル(要差し替え)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>上通アーケード 案内所</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>熊本県熊本市中央区上通町</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>32.8052</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>130.7075</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>案内所内</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>10:00-20:00</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>サンプル(要差し替え)</t>
+          <t>サンプル(座標は概算・要差し替え)</t>
         </is>
       </c>
     </row>
@@ -761,16 +728,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>【AED.xlsx の使い方】</t>
+          <t>【AED.xlsx の使い方(日田市AEDナビ)】</t>
         </is>
       </c>
     </row>
@@ -784,19 +751,26 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>・必須列: 名称 / 緯度 / 経度(10進数の度。例: 32.8063, 130.7058)。他の列は空欄可。</t>
+          <t>・必須列: 名称 / 緯度 / 経度(10進数の度。例: 33.3214, 130.9392)。他の列は空欄可。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>・現在入っている8行は動作確認用のサンプルです(座標は概算)。実際のAED設置場所データに差し替えてください。</t>
+          <t>・現在の7行は動作確認用のサンプルです。実在のAED設置場所とは限らず、座標も概算です。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>・実データは日田市や大分県が公開するAED設置場所一覧、または日本救急医療財団の全国AEDマップ等で確認し、差し替えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>・アプリは最初のシート(AED)のみ読み込みます。</t>
         </is>
